--- a/data/trans_orig/IP1008-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1008-Clase-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2676</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>4757</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>527</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>101685</t>
+          <t>101676</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91467</t>
+          <t>92788</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>196370</t>
+          <t>196576</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>201374</t>
+          <t>201371</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95939</t>
+          <t>96006</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>163016</t>
+          <t>163496</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4842</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4379</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>195891</t>
+          <t>196507</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>398428</t>
+          <t>398473</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t>5428</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>100998</t>
+          <t>100835</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123068</t>
+          <t>122503</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>225955</t>
+          <t>225982</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>653</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6626</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>8259</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11338</t>
+          <t>10781</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>632225</t>
+          <t>632230</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>638210</t>
+          <t>638203</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>677100</t>
+          <t>676344</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>683254</t>
+          <t>683250</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1312121</t>
+          <t>1312678</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1320782</t>
+          <t>1320891</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>4973</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87581</t>
+          <t>87756</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>183638</t>
+          <t>184311</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3492</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4651</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>202619</t>
+          <t>202136</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>223606</t>
+          <t>223622</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>427841</t>
+          <t>427817</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>683</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6247</t>
+          <t>6759</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>144700</t>
+          <t>144189</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135148</t>
+          <t>135137</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>282756</t>
+          <t>282244</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>288284</t>
+          <t>288320</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>70167</t>
+          <t>69623</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>124010</t>
+          <t>123390</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>7733</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>7319</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11686</t>
+          <t>12661</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>666228</t>
+          <t>666348</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>672733</t>
+          <t>672767</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>706276</t>
+          <t>706182</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>712239</t>
+          <t>712246</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1375896</t>
+          <t>1374921</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1384258</t>
+          <t>1384190</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3344</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>677</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>5667</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>100337</t>
+          <t>101159</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>109402</t>
+          <t>109387</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>212745</t>
+          <t>212793</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>217788</t>
+          <t>217783</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>637</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6345</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>217232</t>
+          <t>216957</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>222933</t>
+          <t>222940</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>207874</t>
+          <t>208054</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>427388</t>
+          <t>427231</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>433200</t>
+          <t>433228</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5534</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>130822</t>
+          <t>131024</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>273748</t>
+          <t>273593</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>3098</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3465</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57986</t>
+          <t>57989</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64360</t>
+          <t>64602</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>124456</t>
+          <t>124567</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>2860</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11264</t>
+          <t>11181</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5742</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4291</t>
+          <t>4474</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13621</t>
+          <t>13619</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>660238</t>
+          <t>660321</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>668764</t>
+          <t>668642</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>703995</t>
+          <t>704530</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>709149</t>
+          <t>709737</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1367618</t>
+          <t>1367620</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1376948</t>
+          <t>1376765</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1008-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1008-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1358</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>527</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2676</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2907</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,5%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1358</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4757</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>96187</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>93441</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,79%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>103825</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>101676</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>101445</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,5%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>97,44%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>96187</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>92788</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>95,12%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>296</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>196576</t>
+          <t>196756</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1183,42 +1183,42 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>87389</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1296,52 +1296,52 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>87389</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4259</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>673</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3326</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3371</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3228</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>98659</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>95073</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,32%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,71%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>98659</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>96006</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>163496</t>
+          <t>163353</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1379</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4226</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4991</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,69%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1379</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4042</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1379</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4334</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>301</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>199354</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>196507</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>195742</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,31%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,89%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,51%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>605</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>398473</t>
+          <t>398765</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1390</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>654</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3285</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3263</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1390</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4786</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>651</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>125899</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>123085</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,91%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,7%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>103466</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>100835</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>100857</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,37%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,85%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>96,87%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>125899</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>122503</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,91%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>96,24%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>345</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>225982</t>
+          <t>225872</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>230756</t>
+          <t>230759</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2550,47 +2550,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>74870</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,107 +2780,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3421</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>8190</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>2559</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>6626</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5949</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,1%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>3421</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1353</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>8259</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>5981</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>5981</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>2568</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>10781</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -2893,107 +2893,107 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>681182</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>676413</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>683240</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,5%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>98,8%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,8%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>949</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>636297</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>632230</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>638203</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>632907</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>638211</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,6%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>99,07%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>99,9%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1024</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>681182</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>676344</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>683250</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,5%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>98,79%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1973</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1317478</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1312871</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1320757</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
         <is>
           <t>99,8%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1317478</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1312678</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1320891</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>953</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1029</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3470,47 +3470,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>88439</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3700,107 +3700,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1442</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4973</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5157</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,56%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>5,56%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1442</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4486</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1442</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4529</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -3813,74 +3813,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>91287</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>87756</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>87572</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,44%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,64%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>94,44%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>272</t>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>184311</t>
+          <t>184354</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4156,47 +4156,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>84205</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4391,102 +4391,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3212</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>694</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3492</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3911</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1341</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3242</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4436</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1341</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4675</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -4499,74 +4499,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>226217</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>223652</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,58%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>297</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>204934</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>202136</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>201717</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,3%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,1%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>226217</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>223622</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,57%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>618</t>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>427817</t>
+          <t>428056</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4734,67 +4734,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>1362</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4980</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5368</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4697</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>647</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -4842,74 +4842,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>138495</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>135731</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,04%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,07%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>147807</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>144189</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>143801</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,09%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,66%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>96,4%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>138495</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>135137</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>96,64%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>404</t>
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>282244</t>
+          <t>282862</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>288320</t>
+          <t>288356</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5072,107 +5072,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4006</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>5,41%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>1281</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4415</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4444</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1281</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4559</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -5185,72 +5185,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>72757</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>70032</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>98,27%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>94,59%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>72757</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>69623</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>98,27%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>123390</t>
+          <t>123505</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5420,67 +5420,67 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>3267</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1271</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>7297</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
           <t>3498</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>1314</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>7733</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>1324</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>8005</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>3267</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1255</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>7319</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12661</t>
+          <t>12088</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -5528,72 +5528,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1013</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>710234</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>706204</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>712230</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,54%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>98,98%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>968</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>670583</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>666348</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>672767</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>666076</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>672757</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,48%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>98,85%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1013</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>710234</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>706182</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>712246</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,54%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1374921</t>
+          <t>1375494</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1384190</t>
+          <t>1384145</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -5641,57 +5641,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>973</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6105,47 +6105,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6335,107 +6335,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3634</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1467</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4555</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5138</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,39%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>4,86%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2192</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3359</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5978</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2192</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5667</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -6448,107 +6448,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>112021</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>109112</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,78%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>104247</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>101159</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>100576</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,61%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,69%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>95,14%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>112021</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>109387</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,02%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>216268</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>212482</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>218460</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>97,26%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>216268</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>212793</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>217783</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>99,0%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>97,41%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6791,47 +6791,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -6904,57 +6904,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7021,72 +7021,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2972</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2571</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>637</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6620</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5889</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,15%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2800</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -7134,74 +7134,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>210266</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>207882</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,59%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>221006</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>216957</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>222940</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>217688</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>222956</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,85%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,04%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>210266</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>208054</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,37%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,72%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,67%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>637</t>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>427231</t>
+          <t>427270</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>433228</t>
+          <t>433207</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7364,107 +7364,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1579</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5170</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,16%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,8%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>4,41%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1579</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5689</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -7477,74 +7477,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>134615</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>131024</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>130194</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,84%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,2%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>95,59%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>402</t>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>273593</t>
+          <t>274019</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7712,102 +7712,102 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3193</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4,71%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>617</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3098</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3748</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1253</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3223</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3828</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>4,75%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1253</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4345</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -7820,74 +7820,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>67189</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>64632</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>99,06%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>95,29%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>60470</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>57989</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>57339</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>98,99%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>94,93%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>93,86%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>67189</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>64602</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>99,06%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>95,25%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>184</t>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>124567</t>
+          <t>125084</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8050,72 +8050,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>5646</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>6235</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2860</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>11181</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>2661</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>11400</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,93%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>1949</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>5207</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4474</t>
+          <t>4097</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13619</t>
+          <t>13652</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8163,72 +8163,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1014</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>707788</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>704091</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>709149</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1004</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>665267</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>660321</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>668642</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>660102</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>668841</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,07%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>98,33%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1014</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>707788</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>704530</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1367620</t>
+          <t>1367587</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1376765</t>
+          <t>1377142</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>1013</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1017</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
